--- a/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
+++ b/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="70">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -92,7 +92,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: pressiona opcao “Extract from directory”</t>
+    <t>administrador: pressiona opcao “Extract from dicrtory”</t>
   </si>
   <si>
     <t/>
@@ -101,13 +101,13 @@
     <t>SYSTEM exibe tela de extracao por diretorio</t>
   </si>
   <si>
-    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contem 703 extrações para diversas familias, e pressiona o botao “Extract”</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe na parte inferior da tela uma mensagem indicando que 703 extrações foram realizadas</t>
-  </si>
-  <si>
-    <t>administrador: acessa pagina “Extractions” e seleciona opção para mostrar 50 entradas por página</t>
+    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contem 705 extrações para diversas familias, e pressiona o botao “Extract”</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe na parte inferior da tela uma mensagem indicando que 705 extrações foram realizadas</t>
+  </si>
+  <si>
+    <t>administrador: acessa pagina “Extractions”</t>
   </si>
   <si>
     <t>SYSTEM exibe a lista de extrações com as 50 ultimas entradas. Entrada 1: 14170PP30289943. Entrada 50: 12328PP30166463</t>
@@ -143,7 +143,7 @@
     <t>administrador: seleciona opcao default no campo de filtro “Customer”</t>
   </si>
   <si>
-    <t>SYSTEM atualiza a pagina mostrando todas 703 extrações</t>
+    <t>SYSTEM atualiza a pagina mostrando todas 705 extrações</t>
   </si>
   <si>
     <t>TC3</t>
@@ -218,10 +218,7 @@
     <t>Alternative Flow 7: Extracoes Sequenciais</t>
   </si>
   <si>
-    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contém 703 extrações para diversas família, e pressiona o botão “Extract”</t>
-  </si>
-  <si>
-    <t>administrador: acessa pagina “Extractions”</t>
+    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contém 705 extrações para diversas família, e pressiona o botão “Extract”</t>
   </si>
   <si>
     <t>SYSTEM exibe uma lista com 1510</t>
@@ -1471,13 +1468,13 @@
         <v>5.0</v>
       </c>
       <c r="B90" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s" s="3">
         <v>69</v>
-      </c>
-      <c r="C90" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D90" t="s" s="3">
-        <v>70</v>
       </c>
       <c r="E90" t="s" s="3">
         <v>27</v>

--- a/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
+++ b/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="69">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuário deve estar logado no servidor e extrator com administrador ; Nao existem extrações cadastradas no banco de dados</t>
+    <t>Usuário deve estar logado no servidor e extrator com administrador ; Não existem extrações cadastradas no banco de dados</t>
   </si>
   <si>
     <t>#</t>
@@ -92,43 +92,43 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: pressiona opcao “Extract from dicrtory”</t>
+    <t>administrador: pressiona opção “Extract from dicrtory”</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe tela de extracao por diretorio</t>
-  </si>
-  <si>
-    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contem 705 extrações para diversas familias, e pressiona o botao “Extract”</t>
+    <t>SYSTEM exibe tela de extração por diretório</t>
+  </si>
+  <si>
+    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contém 705 extrações para diversas família, e pressiona o botão “Extract”</t>
   </si>
   <si>
     <t>SYSTEM exibe na parte inferior da tela uma mensagem indicando que 705 extrações foram realizadas</t>
   </si>
   <si>
-    <t>administrador: acessa pagina “Extractions”</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe a lista de extrações com as 50 ultimas entradas. Entrada 1: 14170PP30289943. Entrada 50: 12328PP30166463</t>
-  </si>
-  <si>
-    <t>administrador: seleciona opcao para mostrar 100 entradas por pagina</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe a lista de extrações com as 100 ultimas entradas.</t>
+    <t>administrador: acessa página “Extractions”</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe a lista de extrações com as 50 últimas entradas. Entrada 1: 14170PP30289943. Entrada 50: 12328PP30166463</t>
+  </si>
+  <si>
+    <t>administrador: seleciona opção para mostrar 100 entradas por página</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe a lista de extrações com as 100 últimas entradas.</t>
   </si>
   <si>
     <t>administrador: seleciona o combo box referente ao filtro por “Customer”</t>
   </si>
   <si>
-    <t>SYSTEM exibe as opcoes “Ingenico Brazil” e “Ingenico”</t>
-  </si>
-  <si>
-    <t>administrador: seleciona opcao “Ingenico” no campo de filtro “Customer”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza a pagina mostrando somente 32 extrações</t>
+    <t>SYSTEM exibe as opções “Ingenico Brazil” e “Ingenico”</t>
+  </si>
+  <si>
+    <t>administrador: seleciona opção “Ingenico” no campo de filtro “Customer”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza a página mostrando somente 32 extrações</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -140,10 +140,10 @@
     <t>Alternative Flow 1: Filtro default</t>
   </si>
   <si>
-    <t>administrador: seleciona opcao default no campo de filtro “Customer”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza a pagina mostrando todas 705 extrações</t>
+    <t>administrador: seleciona opção default no campo de filtro “Customer”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza a página mostrando todas 705 extrações</t>
   </si>
   <si>
     <t>TC3</t>
@@ -155,7 +155,7 @@
     <t>administrador: seleciona opção Ingenico Brazil no campo de filtro “Customer”</t>
   </si>
   <si>
-    <t>SYSTEM atualiza a pagina mostrando 673 extracoes</t>
+    <t>SYSTEM atualiza a página mostrando todas 673 extrações</t>
   </si>
   <si>
     <t>TC4</t>
@@ -167,13 +167,13 @@
     <t>administrador: seleciona combo box referente ao filtro por “State”</t>
   </si>
   <si>
-    <t>SYSTEM exibe opcoes “Activated”, “Alert Interruption”, “Deactivated”, “Mockup” e “Error”</t>
-  </si>
-  <si>
-    <t>administrador: seleciona opcao “Activated” no campo de filtro “State”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza pagina mostrando 608 extrações</t>
+    <t>SYSTEM exibe opções “Activated”, “Alert Interruption”, “Deactivated”, “Mockup” e “Error”</t>
+  </si>
+  <si>
+    <t>administrador: seleciona opção “Activated” no campo de filtro “State”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza página mostrando 608 extrações</t>
   </si>
   <si>
     <t>TC5</t>
@@ -182,10 +182,10 @@
     <t>Alternative Flow 4: Filtro “Alert Interruption”</t>
   </si>
   <si>
-    <t>administrador: seleciona opcao “Alert Interruption” no campo de filtro “State”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza pagina mostrando 97 extracoes</t>
+    <t>administrador: seleciona opção “Alert Interruption” no campo de filtro “State”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza página mostrando 97 extrações</t>
   </si>
   <si>
     <t>TC6</t>
@@ -194,10 +194,10 @@
     <t>Alternative Flow 5: Filtro “Mockup”</t>
   </si>
   <si>
-    <t>administrador: seleciona opcao “Mockup” no campo de filtro “State”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza pagina mostrando lista vazia</t>
+    <t>administrador: seleciona opção “Mockup” no campo de filtro “State”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza página mostrando lista vazia</t>
   </si>
   <si>
     <t>TC7</t>
@@ -206,19 +206,16 @@
     <t>Alternative Flow 6: Filtro “Error”</t>
   </si>
   <si>
-    <t>administrador: seleciona opcao “Error” no campo de filtro “State”</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza pagina mostrando extrações associadas aos estados 'Alert Interruption' e 'Mockup'</t>
+    <t>administrador: seleciona opção “Error” no campo de filtro “State”</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza página mostrando extrações associadas aos estados 'Alert Interruption' e 'Mockup'</t>
   </si>
   <si>
     <t>TC8</t>
   </si>
   <si>
-    <t>Alternative Flow 7: Extracoes Sequenciais</t>
-  </si>
-  <si>
-    <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contém 705 extrações para diversas família, e pressiona o botão “Extract”</t>
+    <t>Alternative Flow 7: Extrações Sequenciais</t>
   </si>
   <si>
     <t>SYSTEM exibe uma lista com 1510</t>
@@ -317,7 +314,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="115.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="114.95703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="100.57421875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -1448,7 +1445,7 @@
         <v>4.0</v>
       </c>
       <c r="B89" t="s" s="3">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s" s="3">
         <v>27</v>
@@ -1474,7 +1471,7 @@
         <v>27</v>
       </c>
       <c r="D90" t="s" s="3">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E90" t="s" s="3">
         <v>27</v>

--- a/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
+++ b/output/xlsx/ExtracoesPorDiretorio--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="75">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 8 test case(s)</t>
+    <t>Size: 9 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -104,6 +104,12 @@
     <t>administrador: seleciona pasta “EXTRACT_FILE_IPP320_AKIRA”, que contém 705 extrações para diversas família, e pressiona o botão “Extract”</t>
   </si>
   <si>
+    <t>SYSTEM realiza extrações</t>
+  </si>
+  <si>
+    <t>clock: tempo de execução não passou de 5 segundos</t>
+  </si>
+  <si>
     <t>SYSTEM exibe na parte inferior da tela uma mensagem indicando que 705 extrações foram realizadas</t>
   </si>
   <si>
@@ -137,6 +143,18 @@
     <t>TC2</t>
   </si>
   <si>
+    <t>Alternative Flow 8: Estouro de limite de tempo</t>
+  </si>
+  <si>
+    <t>clock: tempo de execução passou de 5 segundos</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem solicitando que o usuário aguarde</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
     <t>Alternative Flow 1: Filtro default</t>
   </si>
   <si>
@@ -146,7 +164,7 @@
     <t>SYSTEM atualiza a página mostrando todas 705 extrações</t>
   </si>
   <si>
-    <t>TC3</t>
+    <t>TC4</t>
   </si>
   <si>
     <t>Alternative Flow 2: Filtro “Ingenico Brazil”</t>
@@ -158,7 +176,7 @@
     <t>SYSTEM atualiza a página mostrando todas 673 extrações</t>
   </si>
   <si>
-    <t>TC4</t>
+    <t>TC5</t>
   </si>
   <si>
     <t>Alternative Flow 3: Filtro state</t>
@@ -176,7 +194,7 @@
     <t>SYSTEM atualiza página mostrando 608 extrações</t>
   </si>
   <si>
-    <t>TC5</t>
+    <t>TC6</t>
   </si>
   <si>
     <t>Alternative Flow 4: Filtro “Alert Interruption”</t>
@@ -188,7 +206,7 @@
     <t>SYSTEM atualiza página mostrando 97 extrações</t>
   </si>
   <si>
-    <t>TC6</t>
+    <t>TC7</t>
   </si>
   <si>
     <t>Alternative Flow 5: Filtro “Mockup”</t>
@@ -200,7 +218,7 @@
     <t>SYSTEM atualiza página mostrando lista vazia</t>
   </si>
   <si>
-    <t>TC7</t>
+    <t>TC8</t>
   </si>
   <si>
     <t>Alternative Flow 6: Filtro “Error”</t>
@@ -209,13 +227,13 @@
     <t>administrador: seleciona opção “Error” no campo de filtro “State”</t>
   </si>
   <si>
-    <t>SYSTEM atualiza página mostrando extrações associadas aos estados 'Alert Interruption' e 'Mockup'</t>
-  </si>
-  <si>
-    <t>TC8</t>
+    <t>TC9</t>
   </si>
   <si>
     <t>Alternative Flow 7: Extrações Sequenciais</t>
+  </si>
+  <si>
+    <t>clock: verifica se o tempo de execução não passou de 5 segundos</t>
   </si>
   <si>
     <t>SYSTEM exibe uma lista com 1510</t>
@@ -310,7 +328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -534,98 +552,98 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s" s="1">
+      <c r="A16" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B16" t="s" s="3">
         <v>39</v>
       </c>
-      <c r="B16" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s" s="0">
+      <c r="C16" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s" s="3">
         <v>40</v>
       </c>
-      <c r="C19" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s" s="1">
-        <v>14</v>
+      <c r="E16" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E20" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E21" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="B22" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
+    <row r="23">
+      <c r="A23" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B22" t="s" s="2">
+      <c r="B23" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="C23" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D22" t="s" s="2">
+      <c r="D23" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E22" t="s" s="2">
+      <c r="E23" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F22" t="s" s="2">
+      <c r="F23" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B23" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E23" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F23" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s" s="3">
         <v>27</v>
@@ -636,16 +654,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n" s="4">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s" s="3">
         <v>27</v>
@@ -656,16 +674,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n" s="4">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s" s="3">
         <v>27</v>
@@ -676,16 +694,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="B27" t="s" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D27" t="s" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s" s="3">
         <v>27</v>
@@ -696,137 +714,137 @@
     </row>
     <row r="28">
       <c r="A28" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B28" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="4">
         <v>6.0</v>
       </c>
-      <c r="B28" t="s" s="3">
-        <v>42</v>
-      </c>
-      <c r="C28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s" s="3">
-        <v>43</v>
-      </c>
-      <c r="E28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F28" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="1">
+      <c r="B29" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s" s="3">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B30" t="s" s="3">
         <v>39</v>
       </c>
-      <c r="B29" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="C32" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="E33" t="s" s="1">
-        <v>17</v>
+      <c r="C30" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s" s="3">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F30" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B36" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="B37" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="C37" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D35" t="s" s="2">
+      <c r="D37" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E35" t="s" s="2">
+      <c r="E37" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F35" t="s" s="2">
+      <c r="F37" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B36" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F36" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B37" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F37" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n" s="4">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s" s="3">
         <v>27</v>
@@ -837,16 +855,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n" s="4">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="B39" t="s" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D39" t="s" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s" s="3">
         <v>27</v>
@@ -857,16 +875,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n" s="4">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="B40" t="s" s="3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s" s="3">
         <v>27</v>
@@ -877,157 +895,157 @@
     </row>
     <row r="41">
       <c r="A41" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B41" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F41" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B42" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="4">
         <v>6.0</v>
       </c>
-      <c r="B41" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="C41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="E41" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F41" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B42" t="s" s="0">
+      <c r="B43" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="C43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s" s="3">
+        <v>38</v>
+      </c>
+      <c r="E43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B44" t="s" s="3">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s" s="3">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s" s="3">
         <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B45" t="s" s="0">
-        <v>48</v>
-      </c>
-      <c r="C45" t="s" s="1">
+      <c r="B48" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E45" t="s" s="1">
+      <c r="E48" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s" s="1">
+    <row r="49">
+      <c r="A49" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B46" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="E46" t="s" s="1">
+      <c r="B49" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="E49" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="s" s="1">
+    <row r="50">
+      <c r="A50" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="B50" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B48" t="s" s="2">
+      <c r="B51" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="C51" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D48" t="s" s="2">
+      <c r="D51" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E48" t="s" s="2">
+      <c r="E51" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F48" t="s" s="2">
+      <c r="F51" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B49" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D49" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F49" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B50" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D50" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F50" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B51" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D51" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F51" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n" s="4">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="B52" t="s" s="3">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D52" t="s" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E52" t="s" s="3">
         <v>27</v>
@@ -1038,16 +1056,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n" s="4">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="B53" t="s" s="3">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D53" t="s" s="3">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s" s="3">
         <v>27</v>
@@ -1058,178 +1076,257 @@
     </row>
     <row r="54">
       <c r="A54" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B54" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C54" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D54" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E54" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F54" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B55" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C55" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E55" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B56" t="s" s="3">
+        <v>35</v>
+      </c>
+      <c r="C56" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D56" t="s" s="3">
+        <v>36</v>
+      </c>
+      <c r="E56" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F56" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n" s="4">
         <v>6.0</v>
       </c>
-      <c r="B54" t="s" s="3">
+      <c r="B57" t="s" s="3">
+        <v>37</v>
+      </c>
+      <c r="C57" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s" s="3">
+        <v>38</v>
+      </c>
+      <c r="E57" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F57" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B58" t="s" s="3">
         <v>52</v>
       </c>
-      <c r="C54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D54" t="s" s="3">
+      <c r="C58" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s" s="3">
         <v>53</v>
       </c>
-      <c r="E54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F54" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B55" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>54</v>
-      </c>
-      <c r="C58" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E58" t="s" s="1">
-        <v>14</v>
+      <c r="E58" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F58" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="1">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="E59" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B60" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D61" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E61" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F61" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B62" t="s" s="3">
-        <v>56</v>
-      </c>
-      <c r="C62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D62" t="s" s="3">
-        <v>57</v>
-      </c>
-      <c r="E62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s" s="3">
-        <v>27</v>
+      <c r="A62" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C62" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="1">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B63" t="s" s="0">
-        <v>27</v>
+        <v>55</v>
+      </c>
+      <c r="E63" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D65" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B66" t="s" s="0">
-        <v>58</v>
-      </c>
-      <c r="C66" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E66" t="s" s="1">
-        <v>14</v>
+      <c r="A66" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B66" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="E67" t="s" s="1">
-        <v>17</v>
+      <c r="A67" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B67" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D67" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E67" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F67" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B68" t="s" s="0">
-        <v>19</v>
+      <c r="A68" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B68" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D68" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E68" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D69" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F69" t="s" s="2">
-        <v>25</v>
+      <c r="A69" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B69" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C69" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D69" t="s" s="3">
+        <v>34</v>
+      </c>
+      <c r="E69" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F69" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n" s="4">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="B70" t="s" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D70" t="s" s="3">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E70" t="s" s="3">
         <v>27</v>
@@ -1239,252 +1336,494 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B71" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>62</v>
-      </c>
-      <c r="C74" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E74" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s" s="0">
-        <v>63</v>
-      </c>
-      <c r="E75" t="s" s="1">
-        <v>17</v>
+      <c r="A71" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B71" t="s" s="3">
+        <v>56</v>
+      </c>
+      <c r="C71" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D71" t="s" s="3">
+        <v>57</v>
+      </c>
+      <c r="E71" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B72" t="s" s="3">
+        <v>58</v>
+      </c>
+      <c r="C72" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="E72" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F72" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C76" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E77" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B76" t="s" s="0">
+      <c r="B78" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
+    <row r="79">
+      <c r="A79" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B77" t="s" s="2">
+      <c r="B79" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C77" t="s" s="2">
+      <c r="C79" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D77" t="s" s="2">
+      <c r="D79" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E77" t="s" s="2">
+      <c r="E79" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F77" t="s" s="2">
+      <c r="F79" t="s" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n" s="4">
+    <row r="80">
+      <c r="A80" t="n" s="4">
         <v>1.0</v>
       </c>
-      <c r="B78" t="s" s="3">
-        <v>64</v>
-      </c>
-      <c r="C78" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D78" t="s" s="3">
-        <v>65</v>
-      </c>
-      <c r="E78" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F78" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B79" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B82" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="C82" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E82" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="E83" t="s" s="1">
-        <v>17</v>
+      <c r="B80" t="s" s="3">
+        <v>62</v>
+      </c>
+      <c r="C80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E80" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F80" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C84" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="E85" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="B86" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="s" s="2">
+    <row r="87">
+      <c r="A87" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B85" t="s" s="2">
+      <c r="B87" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C85" t="s" s="2">
+      <c r="C87" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D85" t="s" s="2">
+      <c r="D87" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E85" t="s" s="2">
+      <c r="E87" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F85" t="s" s="2">
+      <c r="F87" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B86" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D86" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E86" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F86" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D87" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F87" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B88" t="s" s="3">
+        <v>66</v>
+      </c>
+      <c r="C88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s" s="3">
+        <v>67</v>
+      </c>
+      <c r="E88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="E93" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D95" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B96" t="s" s="3">
+        <v>70</v>
+      </c>
+      <c r="C96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D96" t="s" s="3">
+        <v>67</v>
+      </c>
+      <c r="E96" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F96" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C100" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="E101" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D103" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B104" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D104" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E104" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F104" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B105" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C105" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D105" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E105" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F105" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B88" t="s" s="3">
+      <c r="B106" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C106" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D106" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E106" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F106" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B107" t="s" s="3">
         <v>26</v>
       </c>
-      <c r="C88" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D88" t="s" s="3">
+      <c r="C107" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D107" t="s" s="3">
         <v>28</v>
       </c>
-      <c r="E88" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F88" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B89" t="s" s="3">
+      <c r="E107" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F107" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B108" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="C89" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D89" t="s" s="3">
+      <c r="C108" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D108" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="E89" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F89" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B90" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C90" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D90" t="s" s="3">
-        <v>68</v>
-      </c>
-      <c r="E90" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F90" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="1">
-        <v>39</v>
-      </c>
-      <c r="B91" t="s" s="0">
+      <c r="E108" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F108" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B109" t="s" s="3">
+        <v>73</v>
+      </c>
+      <c r="C109" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D109" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E109" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F109" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B110" t="s" s="3">
+        <v>33</v>
+      </c>
+      <c r="C110" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D110" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="E110" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B111" t="s" s="0">
         <v>27</v>
       </c>
     </row>
